--- a/Excel/InvOperativa_FINAL.xlsx
+++ b/Excel/InvOperativa_FINAL.xlsx
@@ -1,59 +1,97 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rick\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rick\Documents\GitHub\InvestigacionOperativaExcel\yarimashita\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B47C48D7-69DF-4112-A527-99F8079FD360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{75FC1AFD-F82D-4126-A285-D8C2412BE2DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Modelo" sheetId="1" r:id="rId1"/>
     <sheet name="Eficaz" sheetId="4" r:id="rId2"/>
     <sheet name="Acuerdo (Eficiente)" sheetId="6" r:id="rId3"/>
+    <sheet name="Sensibilidad" sheetId="8" r:id="rId4"/>
+    <sheet name="Modelo de Trans" sheetId="7" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="solver_adj" localSheetId="1" hidden="1">Eficaz!$B$3:$B$9</definedName>
+    <definedName name="solver_adj" localSheetId="4" hidden="1">'Modelo de Trans'!$C$12:$E$14</definedName>
     <definedName name="solver_cvg" localSheetId="1" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="4" hidden="1">0.0001</definedName>
     <definedName name="solver_drv" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="4" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="1" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="4" hidden="1">2</definedName>
     <definedName name="solver_est" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="4" hidden="1">1</definedName>
     <definedName name="solver_itr" localSheetId="1" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="4" hidden="1">2147483647</definedName>
     <definedName name="solver_lhs1" localSheetId="1" hidden="1">Eficaz!$B$12:$B$20</definedName>
+    <definedName name="solver_lhs1" localSheetId="4" hidden="1">'Modelo de Trans'!$C$13</definedName>
     <definedName name="solver_lhs2" localSheetId="1" hidden="1">Eficaz!$B$22:$B$24</definedName>
+    <definedName name="solver_lhs2" localSheetId="4" hidden="1">'Modelo de Trans'!$C$15:$E$15</definedName>
     <definedName name="solver_lhs3" localSheetId="1" hidden="1">Eficaz!$B$3:$B$9</definedName>
+    <definedName name="solver_lhs3" localSheetId="4" hidden="1">'Modelo de Trans'!$F$12:$F$14</definedName>
     <definedName name="solver_mip" localSheetId="1" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="4" hidden="1">2147483647</definedName>
     <definedName name="solver_mni" localSheetId="1" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="4" hidden="1">30</definedName>
     <definedName name="solver_mrt" localSheetId="1" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="4" hidden="1">0.075</definedName>
     <definedName name="solver_msl" localSheetId="1" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="4" hidden="1">2</definedName>
     <definedName name="solver_neg" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="4" hidden="1">1</definedName>
     <definedName name="solver_nod" localSheetId="1" hidden="1">2147483647</definedName>
-    <definedName name="solver_num" localSheetId="1" hidden="1">3</definedName>
+    <definedName name="solver_nod" localSheetId="4" hidden="1">2147483647</definedName>
+    <definedName name="solver_num" localSheetId="1" hidden="1">2</definedName>
+    <definedName name="solver_num" localSheetId="4" hidden="1">3</definedName>
     <definedName name="solver_nwt" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="4" hidden="1">1</definedName>
     <definedName name="solver_opt" localSheetId="1" hidden="1">Eficaz!$B$36</definedName>
+    <definedName name="solver_opt" localSheetId="4" hidden="1">'Modelo de Trans'!$J$13</definedName>
     <definedName name="solver_pre" localSheetId="1" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="4" hidden="1">0.000001</definedName>
     <definedName name="solver_rbv" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="4" hidden="1">2</definedName>
     <definedName name="solver_rel1" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_rel1" localSheetId="4" hidden="1">2</definedName>
     <definedName name="solver_rel2" localSheetId="1" hidden="1">3</definedName>
+    <definedName name="solver_rel2" localSheetId="4" hidden="1">2</definedName>
     <definedName name="solver_rel3" localSheetId="1" hidden="1">4</definedName>
+    <definedName name="solver_rel3" localSheetId="4" hidden="1">2</definedName>
     <definedName name="solver_rhs1" localSheetId="1" hidden="1">Eficaz!$D$12:$D$20</definedName>
+    <definedName name="solver_rhs1" localSheetId="4" hidden="1">1</definedName>
     <definedName name="solver_rhs2" localSheetId="1" hidden="1">Eficaz!$D$22:$D$24</definedName>
+    <definedName name="solver_rhs2" localSheetId="4" hidden="1">'Modelo de Trans'!$C$17:$E$17</definedName>
     <definedName name="solver_rhs3" localSheetId="1" hidden="1">"integer"</definedName>
+    <definedName name="solver_rhs3" localSheetId="4" hidden="1">'Modelo de Trans'!$H$12:$H$14</definedName>
     <definedName name="solver_rlx" localSheetId="1" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="4" hidden="1">2</definedName>
     <definedName name="solver_rsd" localSheetId="1" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="4" hidden="1">0</definedName>
     <definedName name="solver_scl" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="4" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="1" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="4" hidden="1">2</definedName>
     <definedName name="solver_ssz" localSheetId="1" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="4" hidden="1">100</definedName>
     <definedName name="solver_tim" localSheetId="1" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="4" hidden="1">2147483647</definedName>
     <definedName name="solver_tol" localSheetId="1" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="4" hidden="1">0.01</definedName>
     <definedName name="solver_typ" localSheetId="1" hidden="1">1</definedName>
+    <definedName name="solver_typ" localSheetId="4" hidden="1">2</definedName>
     <definedName name="solver_val" localSheetId="1" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="4" hidden="1">0</definedName>
     <definedName name="solver_ver" localSheetId="1" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="4" hidden="1">3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -73,7 +111,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="219">
   <si>
     <t>MAKI &amp; RAMEN HOUSE</t>
   </si>
@@ -165,6 +203,9 @@
     <t>Maximizar  Z  =  ingresos diarios por venta (S/)</t>
   </si>
   <si>
+    <t>Z = 22.X1 + 20.X2 + 28.X3 + 25.X4 + 25.X5 + 25.X6 + 15.X7</t>
+  </si>
+  <si>
     <t>Los coeficientes son los precios de venta de cada producto (S/ por unidad):</t>
   </si>
   <si>
@@ -195,57 +236,93 @@
     <t>Salsas (litros)</t>
   </si>
   <si>
+    <t>0.08.X1 + 0.04.X2 + 0.06.X3 + 0.04.X4 + 0.07.X5</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
     <t>Arroz (gramos)</t>
   </si>
   <si>
+    <t>250.(X1 + X2 + X3 + X4 + X5)</t>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
     <t>Salmón (porciones)</t>
   </si>
   <si>
+    <t>X1 + X4 + X5</t>
+  </si>
+  <si>
     <t>4</t>
   </si>
   <si>
     <t>Langostino (porciones)</t>
   </si>
   <si>
+    <t>3.(X1 + X2 + X3 + X4 + X5)</t>
+  </si>
+  <si>
     <t>5</t>
   </si>
   <si>
     <t>Palta (porciones)</t>
   </si>
   <si>
+    <t>X1 + X3 + X5</t>
+  </si>
+  <si>
     <t>6</t>
   </si>
   <si>
     <t>Queso crema (porciones)</t>
   </si>
   <si>
+    <t>X2 + X5</t>
+  </si>
+  <si>
     <t>7</t>
   </si>
   <si>
     <t>Fideos (unidades)</t>
   </si>
   <si>
+    <t>X6 + X7</t>
+  </si>
+  <si>
     <t>8</t>
   </si>
   <si>
     <t>Tiempo de preparación (min)</t>
   </si>
   <si>
+    <t>10.X1 + 10.X2 + 15.X3 + 10.X4 + 10.X5 + 13.X6 + 8.X7</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
     <t>Demanda mínima Maki Acevichado</t>
   </si>
   <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>Demanda mínima Maki Furai</t>
   </si>
   <si>
+    <t>11</t>
+  </si>
+  <si>
     <t>Demanda mínima Ramen Especial</t>
   </si>
   <si>
+    <t>12</t>
+  </si>
+  <si>
     <t>No negatividad de las variables</t>
   </si>
   <si>
@@ -372,6 +449,9 @@
     <t>Interpretación</t>
   </si>
   <si>
+    <t>El consumo de salsas no puede superar 10 litros.</t>
+  </si>
+  <si>
     <t>El arroz disponible limita la producción total de makis.</t>
   </si>
   <si>
@@ -453,13 +533,241 @@
     <t xml:space="preserve"> X ≥ 95%</t>
   </si>
   <si>
-    <t>El consumo de salsas no puede superar 3 litros.</t>
-  </si>
-  <si>
-    <t>Solo X6 utiliza</t>
-  </si>
-  <si>
-    <t>Z = 22.X1 + 20.X2 + 25.X3 + 30.X4 + 28.X5 + 30.X6 + 15.X7</t>
+    <t>Min 3 prov</t>
+  </si>
+  <si>
+    <t>Microsoft Excel 16.0 Sensitivity Report</t>
+  </si>
+  <si>
+    <t>Worksheet: [InvOperativa_FINAL (1).xlsx]Eficaz</t>
+  </si>
+  <si>
+    <t>Report Created: 24/09/2026 20:54:16</t>
+  </si>
+  <si>
+    <t>Variable Cells</t>
+  </si>
+  <si>
+    <t>Cell</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Final</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Reduced</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>Objective</t>
+  </si>
+  <si>
+    <t>Coefficient</t>
+  </si>
+  <si>
+    <t>Allowable</t>
+  </si>
+  <si>
+    <t>Increase</t>
+  </si>
+  <si>
+    <t>Decrease</t>
+  </si>
+  <si>
+    <t>Constraints</t>
+  </si>
+  <si>
+    <t>Shadow</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>Constraint</t>
+  </si>
+  <si>
+    <t>R.H. Side</t>
+  </si>
+  <si>
+    <t>$B$3</t>
+  </si>
+  <si>
+    <t>Cant. Maki Acevichado (unid) Cantidad (unid/día)</t>
+  </si>
+  <si>
+    <t>$B$4</t>
+  </si>
+  <si>
+    <t>Cant. Maki California (unid) Cantidad (unid/día)</t>
+  </si>
+  <si>
+    <t>$B$5</t>
+  </si>
+  <si>
+    <t>Cant. Maki Furai (unid) Cantidad (unid/día)</t>
+  </si>
+  <si>
+    <t>$B$6</t>
+  </si>
+  <si>
+    <t>Cant. Maki Salmón (unid) Cantidad (unid/día)</t>
+  </si>
+  <si>
+    <t>$B$7</t>
+  </si>
+  <si>
+    <t>Cant. Maki Tokyo Roll (unid) Cantidad (unid/día)</t>
+  </si>
+  <si>
+    <t>$B$8</t>
+  </si>
+  <si>
+    <t>Cant. Ramen Especial (unid) Cantidad (unid/día)</t>
+  </si>
+  <si>
+    <t>$B$9</t>
+  </si>
+  <si>
+    <t>Cant. Ramen Clásico (unid) Cantidad (unid/día)</t>
+  </si>
+  <si>
+    <t>$B$12</t>
+  </si>
+  <si>
+    <t>Salsas (L) Uso</t>
+  </si>
+  <si>
+    <t>$B$13</t>
+  </si>
+  <si>
+    <t>Arroz (gramos) Uso</t>
+  </si>
+  <si>
+    <t>$B$14</t>
+  </si>
+  <si>
+    <t>Salmón (porciones) Uso</t>
+  </si>
+  <si>
+    <t>$B$15</t>
+  </si>
+  <si>
+    <t>Langostino (unidad) Uso</t>
+  </si>
+  <si>
+    <t>$B$16</t>
+  </si>
+  <si>
+    <t>Fideos (unidad) Uso</t>
+  </si>
+  <si>
+    <t>$B$17</t>
+  </si>
+  <si>
+    <t>Palta (porcion) Uso</t>
+  </si>
+  <si>
+    <t>$B$18</t>
+  </si>
+  <si>
+    <t>Queso crema (porcion) Uso</t>
+  </si>
+  <si>
+    <t>$B$19</t>
+  </si>
+  <si>
+    <t>Cerdo (porcion) Uso</t>
+  </si>
+  <si>
+    <t>$B$20</t>
+  </si>
+  <si>
+    <t>Tiempo de Preparación (min) Uso</t>
+  </si>
+  <si>
+    <t>$B$22</t>
+  </si>
+  <si>
+    <t>Demanda mínima maki acevichado (unid) Uso</t>
+  </si>
+  <si>
+    <t>$B$23</t>
+  </si>
+  <si>
+    <t>Demanda mínima maki furai (unid) Uso</t>
+  </si>
+  <si>
+    <t>$B$24</t>
+  </si>
+  <si>
+    <t>Demanda mínima ramen especial (unid) Uso</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>PROV 1 (MACRO)</t>
+  </si>
+  <si>
+    <t>PROV 2 (METRO)</t>
+  </si>
+  <si>
+    <t>PROV 3 (MAS)</t>
+  </si>
+  <si>
+    <t>BIMESTRAL</t>
+  </si>
+  <si>
+    <t>kg. Diarios</t>
+  </si>
+  <si>
+    <t>kg. Mensuales</t>
+  </si>
+  <si>
+    <t>COSTOS DE TRANSPORTE (20 sacos)</t>
+  </si>
+  <si>
+    <t>LOCAL 2 (CHILCA) 5</t>
+  </si>
+  <si>
+    <t>LOCAL 3 (GRAU) 7</t>
+  </si>
+  <si>
+    <t>LOCAL 1 (El Tambo) 8</t>
+  </si>
+  <si>
+    <t>Matriz de variable</t>
+  </si>
+  <si>
+    <t>Min Z =</t>
+  </si>
+  <si>
+    <t>=</t>
+  </si>
+  <si>
+    <t>Sensibilidad</t>
+  </si>
+  <si>
+    <t>Precio sombra</t>
+  </si>
+  <si>
+    <t>Costo reducido</t>
+  </si>
+  <si>
+    <t>dias</t>
+  </si>
+  <si>
+    <t>Sacos por Local</t>
   </si>
 </sst>
 </file>
@@ -587,7 +895,9 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="8"/>
+      <b/>
+      <sz val="11"/>
+      <color indexed="18"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -696,7 +1006,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -875,6 +1185,19 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF999999"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF777777"/>
       </left>
       <right style="thin">
@@ -962,32 +1285,142 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="23"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="23"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="23"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="23"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="23"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="13" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="15" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1002,34 +1435,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="16" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1041,44 +1450,30 @@
     <xf numFmtId="0" fontId="17" fillId="16" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="17" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1096,407 +1491,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>5953</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>17859</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2926929</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>208358</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5310A003-876F-C481-C14A-E65151627D08}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3220641" y="8203406"/>
-          <a:ext cx="2920976" cy="190499"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>5953</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>29766</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2952749</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>244078</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A388CA7D-5899-41E8-1229-F51D4F0A4F55}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3220641" y="8501063"/>
-          <a:ext cx="2946796" cy="214312"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>11908</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>29766</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1119188</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>263463</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6BD0D41-BB9B-08E2-B3D6-A54885B25CCA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3226596" y="8786813"/>
-          <a:ext cx="1107280" cy="233697"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>5954</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>17861</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2274093</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>240957</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C89F4E87-FD61-1E41-BB40-0592E3758ECA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3220642" y="9072564"/>
-          <a:ext cx="2268139" cy="223096"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>17860</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>11907</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>621507</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>244079</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3488750-4925-070E-2F58-654D032D4D94}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3232548" y="9780985"/>
-          <a:ext cx="603647" cy="232172"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>29766</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>17859</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1964531</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>226777</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F861213A-05CB-2C36-1585-93B44545CBE1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3244454" y="9346406"/>
-          <a:ext cx="1934765" cy="208918"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>17859</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>17859</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2047874</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>226552</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{801690DF-E8D3-07C4-A4B1-DD8537F5BF7F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3232547" y="9596437"/>
-          <a:ext cx="2030015" cy="208693"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>17860</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>23813</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>345282</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>259148</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99DC8F1E-B932-D171-2D29-9A5A5D27E0A9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3232548" y="10292954"/>
-          <a:ext cx="327422" cy="235335"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>59531</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>59532</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2976562</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>201727</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Picture 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6455E583-4776-7FA3-2FFF-5109C087F5A3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3274219" y="10138173"/>
-          <a:ext cx="2917031" cy="142195"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1796,7 +1790,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.85546875" bestFit="1" customWidth="1"/>
@@ -1808,96 +1802,96 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
+      <c r="A1" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
+      <c r="A2" s="39"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
     </row>
     <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
     </row>
     <row r="6" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="18"/>
+      <c r="B7" s="50"/>
+      <c r="C7" s="50"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="50"/>
+      <c r="F7" s="51"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="19"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="20"/>
+      <c r="A8" s="52"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="39"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="53"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="21"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="23"/>
+      <c r="A9" s="54"/>
+      <c r="B9" s="55"/>
+      <c r="C9" s="55"/>
+      <c r="D9" s="55"/>
+      <c r="E9" s="55"/>
+      <c r="F9" s="56"/>
     </row>
     <row r="13" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
     </row>
     <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="48"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
@@ -2012,48 +2006,48 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="24" t="s">
+      <c r="A24" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
     </row>
     <row r="27" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="30" t="s">
+      <c r="A27" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="B27" s="30"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
+      <c r="B27" s="46"/>
+      <c r="C27" s="46"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="46"/>
     </row>
     <row r="28" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="31" t="s">
+      <c r="A28" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
+      <c r="B28" s="45"/>
+      <c r="C28" s="45"/>
+      <c r="D28" s="45"/>
+      <c r="E28" s="45"/>
     </row>
     <row r="29" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A29" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="29"/>
+      <c r="A29" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" s="41"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="42"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
+      <c r="A30" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" s="39"/>
+      <c r="C30" s="39"/>
+      <c r="D30" s="39"/>
+      <c r="E30" s="39"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
@@ -2063,7 +2057,7 @@
         <v>7</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2073,7 +2067,7 @@
       <c r="B33" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C33" s="5">
+      <c r="C33" s="2">
         <v>22</v>
       </c>
     </row>
@@ -2084,7 +2078,7 @@
       <c r="B34" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C34" s="5">
+      <c r="C34" s="2">
         <v>20</v>
       </c>
     </row>
@@ -2095,8 +2089,8 @@
       <c r="B35" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C35" s="5">
-        <v>25</v>
+      <c r="C35" s="2">
+        <v>28</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2106,8 +2100,8 @@
       <c r="B36" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C36" s="5">
-        <v>30</v>
+      <c r="C36" s="2">
+        <v>25</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2117,8 +2111,8 @@
       <c r="B37" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C37" s="5">
-        <v>28</v>
+      <c r="C37" s="2">
+        <v>25</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -2128,8 +2122,8 @@
       <c r="B38" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C38" s="5">
-        <v>30</v>
+      <c r="C38" s="2">
+        <v>25</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2139,285 +2133,282 @@
       <c r="B39" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C39" s="5">
+      <c r="C39" s="2">
         <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="B41" s="32"/>
-      <c r="C41" s="32"/>
-      <c r="D41" s="32"/>
-      <c r="E41" s="32"/>
-      <c r="F41" s="32"/>
+      <c r="A41" s="43" t="s">
+        <v>33</v>
+      </c>
+      <c r="B41" s="43"/>
+      <c r="C41" s="43"/>
+      <c r="D41" s="43"/>
+      <c r="E41" s="43"/>
+      <c r="F41" s="43"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="B42" s="33" t="s">
+      <c r="A42" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C42" s="33" t="s">
+      <c r="B42" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="33" t="s">
+      <c r="C42" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E42" s="33" t="s">
+      <c r="D42" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="F42" s="33" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="51" t="s">
+      <c r="E42" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="48" t="s">
+      <c r="F42" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C43" s="49"/>
-      <c r="D43" s="54" t="s">
-        <v>72</v>
-      </c>
-      <c r="E43" s="54">
-        <v>3</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="51" t="s">
+      <c r="B43" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B44" s="48" t="s">
+      <c r="C43" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C44" s="49"/>
-      <c r="D44" s="54" t="s">
-        <v>72</v>
-      </c>
-      <c r="E44" s="54">
+      <c r="D43" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E43" s="13">
+        <v>10</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E44" s="13">
         <v>5500</v>
       </c>
-      <c r="F44" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="B45" s="48" t="s">
-        <v>43</v>
-      </c>
-      <c r="C45" s="48"/>
-      <c r="D45" s="54" t="s">
-        <v>72</v>
-      </c>
-      <c r="E45" s="54">
+      <c r="F44" s="7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E45" s="13">
         <v>30</v>
       </c>
-      <c r="F45" s="5" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="51" t="s">
-        <v>44</v>
-      </c>
-      <c r="B46" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="C46" s="48"/>
-      <c r="D46" s="54" t="s">
-        <v>72</v>
-      </c>
-      <c r="E46" s="54">
+      <c r="F45" s="7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E46" s="13">
         <v>70</v>
       </c>
-      <c r="F46" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="51" t="s">
-        <v>46</v>
-      </c>
-      <c r="B47" s="48" t="s">
-        <v>47</v>
-      </c>
-      <c r="C47" s="49"/>
-      <c r="D47" s="54" t="s">
-        <v>72</v>
-      </c>
-      <c r="E47" s="54">
-        <v>100</v>
-      </c>
-      <c r="F47" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="51" t="s">
-        <v>48</v>
-      </c>
-      <c r="B48" s="48" t="s">
-        <v>49</v>
-      </c>
-      <c r="D48" s="54" t="s">
-        <v>72</v>
-      </c>
-      <c r="E48" s="54">
-        <v>100</v>
-      </c>
-      <c r="F48" s="5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="51" t="s">
-        <v>50</v>
-      </c>
-      <c r="B49" s="48" t="s">
+      <c r="F46" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C49" s="48"/>
-      <c r="D49" s="54" t="s">
-        <v>72</v>
-      </c>
-      <c r="E49" s="54">
+      <c r="B47" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E47" s="13">
+        <v>90</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E48" s="13">
+        <v>60</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E49" s="13">
         <v>30</v>
       </c>
-      <c r="F49" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="51" t="s">
-        <v>52</v>
-      </c>
-      <c r="B50" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="C50" s="48"/>
-      <c r="D50" s="54" t="s">
-        <v>72</v>
-      </c>
-      <c r="E50" s="54">
+      <c r="F49" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E50" s="13">
         <v>400</v>
       </c>
-      <c r="F50" s="5" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="52">
-        <v>9</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="C51" s="5"/>
-      <c r="D51" s="54" t="s">
-        <v>72</v>
-      </c>
-      <c r="E51" s="7">
-        <v>50</v>
-      </c>
-      <c r="F51" s="5" t="s">
-        <v>127</v>
+      <c r="F50" s="7" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="B51" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C51" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D51" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="E51" s="16">
+        <v>5</v>
+      </c>
+      <c r="F51" s="17" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="53">
-        <v>10</v>
-      </c>
-      <c r="B52" s="50" t="s">
-        <v>54</v>
-      </c>
-      <c r="C52" s="50" t="s">
-        <v>11</v>
-      </c>
-      <c r="D52" s="55" t="s">
-        <v>76</v>
-      </c>
-      <c r="E52" s="55">
+      <c r="A52" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B52" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C52" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D52" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="E52" s="16">
         <v>5</v>
       </c>
-      <c r="F52" s="34" t="s">
-        <v>106</v>
+      <c r="F52" s="17" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="53">
-        <v>11</v>
-      </c>
-      <c r="B53" s="50" t="s">
-        <v>55</v>
-      </c>
-      <c r="C53" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="D53" s="55" t="s">
-        <v>76</v>
-      </c>
-      <c r="E53" s="55">
+      <c r="A53" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="B53" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C53" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D53" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="E53" s="16">
         <v>5</v>
       </c>
-      <c r="F53" s="34" t="s">
-        <v>107</v>
+      <c r="F53" s="17" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="53">
-        <v>12</v>
-      </c>
-      <c r="B54" s="50" t="s">
-        <v>56</v>
-      </c>
-      <c r="C54" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="D54" s="55" t="s">
-        <v>76</v>
-      </c>
-      <c r="E54" s="55">
-        <v>5</v>
-      </c>
-      <c r="F54" s="34" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="53">
-        <v>13</v>
-      </c>
-      <c r="B55" s="50" t="s">
-        <v>57</v>
-      </c>
-      <c r="C55" s="50" t="s">
-        <v>58</v>
-      </c>
-      <c r="D55" s="55" t="s">
-        <v>76</v>
-      </c>
-      <c r="E55" s="55">
-        <v>0</v>
-      </c>
-      <c r="F55" s="34" t="s">
-        <v>109</v>
+      <c r="A54" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="B54" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C54" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D54" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="E54" s="16">
+        <v>0</v>
+      </c>
+      <c r="F54" s="17" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A28:E28"/>
     <mergeCell ref="A1:F2"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A6:F6"/>
@@ -2425,14 +2416,14 @@
     <mergeCell ref="A24:D24"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A27:E27"/>
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A29:E29"/>
     <mergeCell ref="A41:F41"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A27:E27"/>
   </mergeCells>
-  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2441,807 +2432,810 @@
   <dimension ref="A1:J45"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" customWidth="1"/>
     <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.140625" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.28515625" customWidth="1"/>
     <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.5703125" customWidth="1"/>
     <col min="10" max="10" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="38"/>
+      <c r="A1" s="59" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="60"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="62"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="39" t="s">
-        <v>59</v>
-      </c>
-      <c r="B2" s="39" t="s">
-        <v>110</v>
+      <c r="A2" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B3" s="6">
+      <c r="A3" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="8">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B4" s="6">
+      <c r="A4" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B5" s="6">
+      <c r="A5" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" s="8">
         <v>5</v>
       </c>
-      <c r="F5" s="39" t="s">
-        <v>116</v>
-      </c>
-      <c r="G5" s="40" t="s">
-        <v>117</v>
+      <c r="F5" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" s="6">
+      <c r="A6" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="8">
         <v>12</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="G6" s="47" t="s">
-        <v>122</v>
+      <c r="F6" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B7" s="6">
-        <v>0</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="G7" s="47" t="s">
-        <v>123</v>
+      <c r="A7" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" s="8">
+        <v>0</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="G7" s="24" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B8" s="6">
-        <v>15</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="G8" s="47" t="s">
-        <v>124</v>
+      <c r="A8" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="8">
+        <v>15.4</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="G8" s="24" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B9" s="6">
-        <v>0</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="G9" s="47" t="s">
-        <v>125</v>
+      <c r="A9" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="8">
+        <v>0</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G9" s="24" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="39" t="s">
-        <v>67</v>
-      </c>
-      <c r="B11" s="40" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" s="40" t="s">
-        <v>69</v>
-      </c>
-      <c r="D11" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="E11" s="39" t="s">
-        <v>70</v>
-      </c>
-      <c r="F11" s="41" t="s">
-        <v>112</v>
-      </c>
-      <c r="G11" s="41" t="s">
-        <v>113</v>
-      </c>
-      <c r="H11" s="42" t="s">
-        <v>115</v>
+      <c r="A11" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B12" s="8">
+      <c r="A12" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" s="9">
         <f>SUMPRODUCT(B$28:B$34,$B$3:$B$9)</f>
         <v>1.18</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D12" s="8">
+      <c r="C12" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D12" s="9">
         <v>3</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="10">
         <f>B12/D12</f>
         <v>0.39333333333333331</v>
       </c>
-      <c r="F12" s="5" t="str">
+      <c r="F12" s="7" t="str">
         <f>IF(B12&lt;=D12,"✓ OK","✗ EXCEDE")</f>
         <v>✓ OK</v>
       </c>
-      <c r="G12" s="45" t="str">
+      <c r="G12" s="22" t="str">
         <f>IF(E12="","",IF(E12&gt;=0.95,"🔴 Crítico",IF(E12&gt;=0.8,"🟢 Alto",IF(E12&gt;=0.5,"🟡 Medio","⚪ Bajo"))))</f>
         <v>⚪ Bajo</v>
       </c>
-      <c r="H12" s="46" t="str">
+      <c r="H12" s="23" t="str">
         <f>IF(E12="","",IF(E12&gt;=0.95,"Recomienda aumentar",IF(E12&gt;=0.8,"Revisar",IF(E12&gt;=0.5,"Mantener","Se recomienda reducir"))))</f>
         <v>Se recomienda reducir</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="8">
+      <c r="A13" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="26">
         <f>SUMPRODUCT(C$28:C$34,$B$3:$B$9)</f>
         <v>5500</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D13" s="8">
+      <c r="C13" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="D13" s="26">
         <v>5500</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="27">
         <f>B13/D13</f>
         <v>1</v>
       </c>
-      <c r="F13" s="5" t="str">
+      <c r="F13" s="17" t="str">
         <f>IF(B13&lt;=D13,"✓ OK","✗ EXCEDE")</f>
         <v>✓ OK</v>
       </c>
-      <c r="G13" s="45" t="str">
+      <c r="G13" s="28" t="str">
         <f>IF(E13="","",IF(E13&gt;=0.95,"🔴 Crítico",IF(E13&gt;=0.8,"🟢 Alto",IF(E13&gt;=0.5,"🟡 Medio","⚪ Bajo"))))</f>
         <v>🔴 Crítico</v>
       </c>
-      <c r="H13" s="46" t="str">
+      <c r="H13" s="29" t="str">
         <f>IF(E13="","",IF(E13&gt;=0.95,"Recomienda aumentar",IF(E13&gt;=0.8,"Revisar",IF(E13&gt;=0.5,"Mantener","Se recomienda reducir"))))</f>
         <v>Recomienda aumentar</v>
       </c>
+      <c r="J13" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="8">
+      <c r="A14" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="9">
         <f>SUMPRODUCT(D$28:D$34,$B$3:$B$9)</f>
         <v>17</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D14" s="8">
+      <c r="C14" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D14" s="9">
         <v>30</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="10">
         <f t="shared" ref="E14:E16" si="0">B14/D14</f>
         <v>0.56666666666666665</v>
       </c>
-      <c r="F14" s="5" t="str">
+      <c r="F14" s="7" t="str">
         <f t="shared" ref="F14:F20" si="1">IF(B14&lt;=D14,"✓ OK","✗ EXCEDE")</f>
         <v>✓ OK</v>
       </c>
-      <c r="G14" s="45" t="str">
+      <c r="G14" s="22" t="str">
         <f t="shared" ref="G14:G20" si="2">IF(E14="","",IF(E14&gt;=0.95,"🔴 Crítico",IF(E14&gt;=0.8,"🟢 Alto",IF(E14&gt;=0.5,"🟡 Medio","⚪ Bajo"))))</f>
         <v>🟡 Medio</v>
       </c>
-      <c r="H14" s="46" t="str">
+      <c r="H14" s="23" t="str">
         <f t="shared" ref="H14:H20" si="3">IF(E14="","",IF(E14&gt;=0.95,"Recomienda aumentar",IF(E14&gt;=0.8,"Revisar",IF(E14&gt;=0.5,"Mantener","Se recomienda reducir"))))</f>
         <v>Mantener</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="B15" s="8">
+      <c r="A15" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="B15" s="9">
         <f>SUMPRODUCT(E$28:E$34,$B$3:$B$9)</f>
         <v>66</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D15" s="8">
+      <c r="C15" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D15" s="9">
         <v>70</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="10">
         <f t="shared" si="0"/>
         <v>0.94285714285714284</v>
       </c>
-      <c r="F15" s="5" t="str">
+      <c r="F15" s="7" t="str">
         <f t="shared" si="1"/>
         <v>✓ OK</v>
       </c>
-      <c r="G15" s="45" t="str">
+      <c r="G15" s="25" t="str">
         <f>IF(E15="","",IF(E15&gt;=0.95,"🔴 Crítico",IF(E15&gt;=0.8,"🟢 Alto",IF(E15&gt;=0.5,"🟡 Medio","⚪ Bajo"))))</f>
         <v>🟢 Alto</v>
       </c>
-      <c r="H15" s="46" t="str">
+      <c r="H15" s="23" t="str">
         <f t="shared" si="3"/>
         <v>Revisar</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B16" s="8">
+      <c r="A16" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" s="9">
         <f>SUMPRODUCT(F$28:F$34,$B$3:$B$9)</f>
-        <v>15</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D16" s="8">
+        <v>15.4</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" s="9">
         <v>30</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="10">
         <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="F16" s="5" t="str">
+        <v>0.51333333333333331</v>
+      </c>
+      <c r="F16" s="7" t="str">
         <f t="shared" si="1"/>
         <v>✓ OK</v>
       </c>
-      <c r="G16" s="45" t="str">
+      <c r="G16" s="22" t="str">
         <f t="shared" si="2"/>
         <v>🟡 Medio</v>
       </c>
-      <c r="H16" s="46" t="str">
+      <c r="H16" s="23" t="str">
         <f t="shared" si="3"/>
         <v>Mantener</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B17" s="8">
+      <c r="A17" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B17" s="9">
         <f>SUMPRODUCT(G$28:G$34,$B$3:$B$9)</f>
         <v>66</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D17" s="8">
+      <c r="C17" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D17" s="9">
         <v>100</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="10">
         <f>B17/D17</f>
         <v>0.66</v>
       </c>
-      <c r="F17" s="5" t="str">
+      <c r="F17" s="7" t="str">
         <f t="shared" si="1"/>
         <v>✓ OK</v>
       </c>
-      <c r="G17" s="45" t="str">
+      <c r="G17" s="22" t="str">
         <f t="shared" si="2"/>
         <v>🟡 Medio</v>
       </c>
-      <c r="H17" s="46" t="str">
+      <c r="H17" s="23" t="str">
         <f t="shared" si="3"/>
         <v>Mantener</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="B18" s="8">
+      <c r="A18" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B18" s="9">
         <f>SUMPRODUCT(H$28:H$34,$B$3:$B$9)</f>
         <v>66</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D18" s="8">
+      <c r="C18" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D18" s="9">
         <v>100</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="10">
         <f>B18/D18</f>
         <v>0.66</v>
       </c>
-      <c r="F18" s="5" t="str">
+      <c r="F18" s="7" t="str">
         <f t="shared" si="1"/>
         <v>✓ OK</v>
       </c>
-      <c r="G18" s="45" t="str">
+      <c r="G18" s="22" t="str">
         <f t="shared" si="2"/>
         <v>🟡 Medio</v>
       </c>
-      <c r="H18" s="46" t="str">
+      <c r="H18" s="23" t="str">
         <f t="shared" si="3"/>
         <v>Mantener</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="B19" s="8">
+      <c r="A19" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="B19" s="9">
         <f>SUMPRODUCT(I$28:I$34,$B$3:$B$9)</f>
-        <v>45</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D19" s="8">
+        <v>46.2</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D19" s="9">
         <v>50</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="10">
         <f>B19/D19</f>
-        <v>0.9</v>
-      </c>
-      <c r="F19" s="5" t="str">
+        <v>0.92400000000000004</v>
+      </c>
+      <c r="F19" s="7" t="str">
         <f t="shared" si="1"/>
         <v>✓ OK</v>
       </c>
-      <c r="G19" s="45" t="str">
+      <c r="G19" s="25" t="str">
         <f t="shared" si="2"/>
         <v>🟢 Alto</v>
       </c>
-      <c r="H19" s="46" t="str">
+      <c r="H19" s="23" t="str">
         <f t="shared" si="3"/>
         <v>Revisar</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B20" s="8">
+      <c r="A20" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" s="9">
         <f>SUMPRODUCT(J$28:J$34,$B$3:$B$9)</f>
-        <v>494</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D20" s="8">
         <v>500</v>
       </c>
-      <c r="E20" s="9">
+      <c r="C20" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D20" s="9">
+        <v>500</v>
+      </c>
+      <c r="E20" s="10">
         <f>B20/D20</f>
-        <v>0.98799999999999999</v>
-      </c>
-      <c r="F20" s="5" t="str">
+        <v>1</v>
+      </c>
+      <c r="F20" s="7" t="str">
         <f t="shared" si="1"/>
         <v>✓ OK</v>
       </c>
-      <c r="G20" s="45" t="str">
+      <c r="G20" s="25" t="str">
         <f t="shared" si="2"/>
         <v>🔴 Crítico</v>
       </c>
-      <c r="H20" s="46" t="str">
+      <c r="H20" s="23" t="str">
         <f t="shared" si="3"/>
         <v>Recomienda aumentar</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B22" s="8">
+      <c r="A22" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" s="9">
         <f>B3</f>
         <v>5</v>
       </c>
-      <c r="C22" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="D22" s="8">
+      <c r="C22" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="D22" s="9">
         <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B23" s="8">
+      <c r="A23" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B23" s="9">
         <f>B5</f>
         <v>5</v>
       </c>
-      <c r="C23" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="D23" s="8">
+      <c r="C23" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="D23" s="9">
         <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B24" s="8">
+      <c r="A24" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B24" s="9">
         <f>B8</f>
+        <v>15.4</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="D24" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="20" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="C27" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="F27" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="G27" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="H27" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="I27" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="J27" s="18" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" s="7">
+        <v>0.08</v>
+      </c>
+      <c r="C28" s="7">
+        <v>250</v>
+      </c>
+      <c r="D28" s="7">
+        <v>1</v>
+      </c>
+      <c r="E28" s="7">
+        <v>3</v>
+      </c>
+      <c r="F28" s="7">
+        <v>0</v>
+      </c>
+      <c r="G28" s="7">
+        <v>3</v>
+      </c>
+      <c r="H28" s="7">
+        <v>3</v>
+      </c>
+      <c r="I28" s="7">
+        <v>0</v>
+      </c>
+      <c r="J28" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="C29" s="7">
+        <v>250</v>
+      </c>
+      <c r="D29" s="7">
+        <v>0</v>
+      </c>
+      <c r="E29" s="7">
+        <v>3</v>
+      </c>
+      <c r="F29" s="7">
+        <v>0</v>
+      </c>
+      <c r="G29" s="7">
+        <v>3</v>
+      </c>
+      <c r="H29" s="7">
+        <v>3</v>
+      </c>
+      <c r="I29" s="7">
+        <v>0</v>
+      </c>
+      <c r="J29" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B30" s="7">
+        <v>0.06</v>
+      </c>
+      <c r="C30" s="7">
+        <v>250</v>
+      </c>
+      <c r="D30" s="7">
+        <v>0</v>
+      </c>
+      <c r="E30" s="7">
+        <v>3</v>
+      </c>
+      <c r="F30" s="7">
+        <v>0</v>
+      </c>
+      <c r="G30" s="7">
+        <v>3</v>
+      </c>
+      <c r="H30" s="7">
+        <v>3</v>
+      </c>
+      <c r="I30" s="7">
+        <v>0</v>
+      </c>
+      <c r="J30" s="7">
         <v>15</v>
       </c>
-      <c r="C24" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="D24" s="8">
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B31" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="C31" s="7">
+        <v>250</v>
+      </c>
+      <c r="D31" s="7">
+        <v>1</v>
+      </c>
+      <c r="E31" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="41" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="B27" s="39" t="s">
-        <v>71</v>
-      </c>
-      <c r="C27" s="39" t="s">
-        <v>80</v>
-      </c>
-      <c r="D27" s="39" t="s">
-        <v>93</v>
-      </c>
-      <c r="E27" s="39" t="s">
-        <v>81</v>
-      </c>
-      <c r="F27" s="39" t="s">
-        <v>82</v>
-      </c>
-      <c r="G27" s="39" t="s">
-        <v>96</v>
-      </c>
-      <c r="H27" s="39" t="s">
+      <c r="F31" s="7">
+        <v>0</v>
+      </c>
+      <c r="G31" s="7">
+        <v>3</v>
+      </c>
+      <c r="H31" s="7">
+        <v>3</v>
+      </c>
+      <c r="I31" s="7">
+        <v>0</v>
+      </c>
+      <c r="J31" s="7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B32" s="7">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="C32" s="7">
+        <v>250</v>
+      </c>
+      <c r="D32" s="7">
+        <v>1</v>
+      </c>
+      <c r="E32" s="7">
+        <v>3</v>
+      </c>
+      <c r="F32" s="7">
+        <v>0</v>
+      </c>
+      <c r="G32" s="7">
+        <v>3</v>
+      </c>
+      <c r="H32" s="7">
+        <v>3</v>
+      </c>
+      <c r="I32" s="7">
+        <v>0</v>
+      </c>
+      <c r="J32" s="7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B33" s="7">
+        <v>0</v>
+      </c>
+      <c r="C33" s="7">
+        <v>0</v>
+      </c>
+      <c r="D33" s="7">
+        <v>0</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0</v>
+      </c>
+      <c r="F33" s="7">
+        <v>1</v>
+      </c>
+      <c r="G33" s="7">
+        <v>0</v>
+      </c>
+      <c r="H33" s="7">
+        <v>0</v>
+      </c>
+      <c r="I33" s="7">
+        <v>3</v>
+      </c>
+      <c r="J33" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B34" s="7">
+        <v>0</v>
+      </c>
+      <c r="C34" s="7">
+        <v>1</v>
+      </c>
+      <c r="D34" s="7">
+        <v>0</v>
+      </c>
+      <c r="E34" s="7">
+        <v>0</v>
+      </c>
+      <c r="F34" s="7">
+        <v>1</v>
+      </c>
+      <c r="G34" s="7">
+        <v>0</v>
+      </c>
+      <c r="H34" s="7">
+        <v>0</v>
+      </c>
+      <c r="I34" s="7">
+        <v>0</v>
+      </c>
+      <c r="J34" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="I27" s="39" t="s">
-        <v>95</v>
-      </c>
-      <c r="J27" s="39" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B28" s="5">
-        <v>0.08</v>
-      </c>
-      <c r="C28" s="5">
-        <v>250</v>
-      </c>
-      <c r="D28" s="5">
-        <v>1</v>
-      </c>
-      <c r="E28" s="5">
-        <v>3</v>
-      </c>
-      <c r="F28" s="5">
-        <v>0</v>
-      </c>
-      <c r="G28" s="5">
-        <v>3</v>
-      </c>
-      <c r="H28" s="5">
-        <v>3</v>
-      </c>
-      <c r="I28" s="5">
-        <v>0</v>
-      </c>
-      <c r="J28" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B29" s="5">
-        <v>0.04</v>
-      </c>
-      <c r="C29" s="5">
-        <v>250</v>
-      </c>
-      <c r="D29" s="5">
-        <v>0</v>
-      </c>
-      <c r="E29" s="5">
-        <v>3</v>
-      </c>
-      <c r="F29" s="5">
-        <v>0</v>
-      </c>
-      <c r="G29" s="5">
-        <v>3</v>
-      </c>
-      <c r="H29" s="5">
-        <v>3</v>
-      </c>
-      <c r="I29" s="5">
-        <v>0</v>
-      </c>
-      <c r="J29" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B30" s="5">
-        <v>0.06</v>
-      </c>
-      <c r="C30" s="5">
-        <v>250</v>
-      </c>
-      <c r="D30" s="5">
-        <v>0</v>
-      </c>
-      <c r="E30" s="5">
-        <v>3</v>
-      </c>
-      <c r="F30" s="5">
-        <v>0</v>
-      </c>
-      <c r="G30" s="5">
-        <v>3</v>
-      </c>
-      <c r="H30" s="5">
-        <v>3</v>
-      </c>
-      <c r="I30" s="5">
-        <v>0</v>
-      </c>
-      <c r="J30" s="5">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
+      <c r="B36" s="12">
+        <f>SUMPRODUCT(B3:B9,B39:B45)</f>
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="11"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="63" t="s">
+        <v>98</v>
+      </c>
+      <c r="B38" s="64"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B39" s="7">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="B40" s="7">
         <v>20</v>
       </c>
-      <c r="B31" s="5">
-        <v>0.04</v>
-      </c>
-      <c r="C31" s="5">
-        <v>250</v>
-      </c>
-      <c r="D31" s="5">
-        <v>1</v>
-      </c>
-      <c r="E31" s="5">
-        <v>3</v>
-      </c>
-      <c r="F31" s="5">
-        <v>0</v>
-      </c>
-      <c r="G31" s="5">
-        <v>3</v>
-      </c>
-      <c r="H31" s="5">
-        <v>3</v>
-      </c>
-      <c r="I31" s="5">
-        <v>0</v>
-      </c>
-      <c r="J31" s="5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B32" s="5">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="C32" s="5">
-        <v>250</v>
-      </c>
-      <c r="D32" s="5">
-        <v>1</v>
-      </c>
-      <c r="E32" s="5">
-        <v>3</v>
-      </c>
-      <c r="F32" s="5">
-        <v>0</v>
-      </c>
-      <c r="G32" s="5">
-        <v>3</v>
-      </c>
-      <c r="H32" s="5">
-        <v>3</v>
-      </c>
-      <c r="I32" s="5">
-        <v>0</v>
-      </c>
-      <c r="J32" s="5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B33" s="5">
-        <v>0</v>
-      </c>
-      <c r="C33" s="5">
-        <v>0</v>
-      </c>
-      <c r="D33" s="5">
-        <v>0</v>
-      </c>
-      <c r="E33" s="5">
-        <v>0</v>
-      </c>
-      <c r="F33" s="5">
-        <v>1</v>
-      </c>
-      <c r="G33" s="5">
-        <v>0</v>
-      </c>
-      <c r="H33" s="5">
-        <v>0</v>
-      </c>
-      <c r="I33" s="5">
-        <v>3</v>
-      </c>
-      <c r="J33" s="5">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B34" s="5">
-        <v>0</v>
-      </c>
-      <c r="C34" s="5">
-        <v>0</v>
-      </c>
-      <c r="D34" s="5">
-        <v>0</v>
-      </c>
-      <c r="E34" s="5">
-        <v>0</v>
-      </c>
-      <c r="F34" s="5">
-        <v>1</v>
-      </c>
-      <c r="G34" s="5">
-        <v>0</v>
-      </c>
-      <c r="H34" s="5">
-        <v>0</v>
-      </c>
-      <c r="I34" s="5">
-        <v>0</v>
-      </c>
-      <c r="J34" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="39" t="s">
-        <v>84</v>
-      </c>
-      <c r="B36" s="11">
-        <f>SUMPRODUCT(B3:B9,B39:B45)</f>
-        <v>1045</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="10"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="43" t="s">
-        <v>85</v>
-      </c>
-      <c r="B38" s="44"/>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="B39" s="5">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="B40" s="5">
-        <v>20</v>
-      </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="B41" s="5">
+      <c r="A41" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B41" s="7">
         <v>25</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="B42" s="5">
+      <c r="A42" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B42" s="7">
         <v>30</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="B43" s="5">
+      <c r="A43" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B43" s="7">
         <v>28</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="B44" s="5">
+      <c r="A44" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="B44" s="7">
         <v>30</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="B45" s="5">
+      <c r="A45" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B45" s="7">
         <v>15</v>
       </c>
     </row>
@@ -3257,9 +3251,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60D40C97-5F45-4A38-A9B0-9D3FB3D1C47C}">
   <dimension ref="A1:J45"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.42578125" customWidth="1"/>
     <col min="4" max="4" width="14.5703125" customWidth="1"/>
@@ -3272,795 +3266,795 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="38"/>
+      <c r="A1" s="59" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" s="60"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="62"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="39" t="s">
-        <v>59</v>
-      </c>
-      <c r="B2" s="39" t="s">
-        <v>110</v>
+      <c r="A2" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B3" s="6">
+      <c r="A3" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="8">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B4" s="6">
+      <c r="A4" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B5" s="6">
+      <c r="A5" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" s="8">
         <v>5</v>
       </c>
-      <c r="F5" s="39" t="s">
-        <v>116</v>
-      </c>
-      <c r="G5" s="40" t="s">
-        <v>117</v>
+      <c r="F5" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" s="6">
+      <c r="A6" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="8">
         <v>4</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="G6" s="47" t="s">
-        <v>122</v>
+      <c r="F6" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B7" s="6">
+      <c r="A7" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" s="8">
         <v>1</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="G7" s="47" t="s">
-        <v>123</v>
+      <c r="F7" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="G7" s="24" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B8" s="6">
+      <c r="A8" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="8">
         <v>9</v>
       </c>
-      <c r="F8" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="G8" s="47" t="s">
-        <v>124</v>
+      <c r="F8" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="G8" s="24" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B9" s="6">
+      <c r="A9" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="8">
         <v>12</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="G9" s="47" t="s">
-        <v>125</v>
+      <c r="F9" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G9" s="24" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="39" t="s">
-        <v>67</v>
-      </c>
-      <c r="B11" s="40" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" s="40" t="s">
-        <v>69</v>
-      </c>
-      <c r="D11" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="E11" s="39" t="s">
-        <v>70</v>
-      </c>
-      <c r="F11" s="41" t="s">
-        <v>112</v>
-      </c>
-      <c r="G11" s="41" t="s">
-        <v>113</v>
-      </c>
-      <c r="H11" s="42" t="s">
-        <v>115</v>
+      <c r="A11" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B12" s="8">
+      <c r="A12" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" s="9">
         <f>SUMPRODUCT(B$28:B$34,$B$3:$B$9)</f>
         <v>1.37</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D12" s="8">
+      <c r="C12" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D12" s="9">
         <v>3</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="10">
         <f>B12/D12</f>
         <v>0.45666666666666672</v>
       </c>
-      <c r="F12" s="5" t="str">
+      <c r="F12" s="7" t="str">
         <f>IF(B12&lt;=D12,"✓ OK","✗ EXCEDE")</f>
         <v>✓ OK</v>
       </c>
-      <c r="G12" s="45" t="str">
+      <c r="G12" s="22" t="str">
         <f>IF(E12="","",IF(E12&gt;=0.95,"🔴 Crítico",IF(E12&gt;=0.8,"🟢 Alto",IF(E12&gt;=0.5,"🟡 Medio","⚪ Bajo"))))</f>
         <v>⚪ Bajo</v>
       </c>
-      <c r="H12" s="46" t="str">
+      <c r="H12" s="23" t="str">
         <f>IF(E12="","",IF(E12&gt;=0.95,"Recomienda aumentar",IF(E12&gt;=0.8,"Revisar",IF(E12&gt;=0.5,"Mantener","Se recomienda reducir"))))</f>
         <v>Se recomienda reducir</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="8">
+      <c r="A13" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="9">
         <f>SUMPRODUCT(C$28:C$34,$B$3:$B$9)</f>
-        <v>5250</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D13" s="8">
+        <v>5262</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D13" s="9">
         <v>5500</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="10">
         <f>B13/D13</f>
-        <v>0.95454545454545459</v>
-      </c>
-      <c r="F13" s="5" t="str">
+        <v>0.95672727272727276</v>
+      </c>
+      <c r="F13" s="7" t="str">
         <f>IF(B13&lt;=D13,"✓ OK","✗ EXCEDE")</f>
         <v>✓ OK</v>
       </c>
-      <c r="G13" s="45" t="str">
+      <c r="G13" s="25" t="str">
         <f>IF(E13="","",IF(E13&gt;=0.95,"🔴 Crítico",IF(E13&gt;=0.8,"🟢 Alto",IF(E13&gt;=0.5,"🟡 Medio","⚪ Bajo"))))</f>
         <v>🔴 Crítico</v>
       </c>
-      <c r="H13" s="46" t="str">
+      <c r="H13" s="23" t="str">
         <f>IF(E13="","",IF(E13&gt;=0.95,"Recomienda aumentar",IF(E13&gt;=0.8,"Revisar",IF(E13&gt;=0.5,"Mantener","Se recomienda reducir"))))</f>
         <v>Recomienda aumentar</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="8">
+      <c r="A14" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="9">
         <f>SUMPRODUCT(D$28:D$34,$B$3:$B$9)</f>
         <v>15</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D14" s="8">
+      <c r="C14" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D14" s="9">
         <v>30</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="10">
         <f t="shared" ref="E14:E16" si="0">B14/D14</f>
         <v>0.5</v>
       </c>
-      <c r="F14" s="5" t="str">
+      <c r="F14" s="7" t="str">
         <f t="shared" ref="F14:F20" si="1">IF(B14&lt;=D14,"✓ OK","✗ EXCEDE")</f>
         <v>✓ OK</v>
       </c>
-      <c r="G14" s="45" t="str">
+      <c r="G14" s="22" t="str">
         <f t="shared" ref="G14:G20" si="2">IF(E14="","",IF(E14&gt;=0.95,"🔴 Crítico",IF(E14&gt;=0.8,"🟢 Alto",IF(E14&gt;=0.5,"🟡 Medio","⚪ Bajo"))))</f>
         <v>🟡 Medio</v>
       </c>
-      <c r="H14" s="46" t="str">
+      <c r="H14" s="23" t="str">
         <f t="shared" ref="H14:H20" si="3">IF(E14="","",IF(E14&gt;=0.95,"Recomienda aumentar",IF(E14&gt;=0.8,"Revisar",IF(E14&gt;=0.5,"Mantener","Se recomienda reducir"))))</f>
         <v>Mantener</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="B15" s="8">
+      <c r="A15" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="B15" s="9">
         <f>SUMPRODUCT(E$28:E$34,$B$3:$B$9)</f>
         <v>63</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D15" s="8">
+      <c r="C15" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D15" s="9">
         <v>70</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="10">
         <f t="shared" si="0"/>
         <v>0.9</v>
       </c>
-      <c r="F15" s="5" t="str">
+      <c r="F15" s="7" t="str">
         <f t="shared" si="1"/>
         <v>✓ OK</v>
       </c>
-      <c r="G15" s="45" t="str">
+      <c r="G15" s="25" t="str">
         <f>IF(E15="","",IF(E15&gt;=0.95,"🔴 Crítico",IF(E15&gt;=0.8,"🟢 Alto",IF(E15&gt;=0.5,"🟡 Medio","⚪ Bajo"))))</f>
         <v>🟢 Alto</v>
       </c>
-      <c r="H15" s="46" t="str">
+      <c r="H15" s="23" t="str">
         <f t="shared" si="3"/>
         <v>Revisar</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B16" s="8">
+      <c r="A16" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" s="9">
         <f>SUMPRODUCT(F$28:F$34,$B$3:$B$9)</f>
         <v>21</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D16" s="8">
+      <c r="C16" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" s="9">
         <v>30</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="10">
         <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
-      <c r="F16" s="5" t="str">
+      <c r="F16" s="7" t="str">
         <f t="shared" si="1"/>
         <v>✓ OK</v>
       </c>
-      <c r="G16" s="45" t="str">
+      <c r="G16" s="22" t="str">
         <f t="shared" si="2"/>
         <v>🟡 Medio</v>
       </c>
-      <c r="H16" s="46" t="str">
+      <c r="H16" s="23" t="str">
         <f t="shared" si="3"/>
         <v>Mantener</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B17" s="8">
+      <c r="A17" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B17" s="9">
         <f>SUMPRODUCT(G$28:G$34,$B$3:$B$9)</f>
         <v>63</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D17" s="8">
+      <c r="C17" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D17" s="9">
         <v>100</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="10">
         <f>B17/D17</f>
         <v>0.63</v>
       </c>
-      <c r="F17" s="5" t="str">
+      <c r="F17" s="7" t="str">
         <f t="shared" si="1"/>
         <v>✓ OK</v>
       </c>
-      <c r="G17" s="45" t="str">
+      <c r="G17" s="22" t="str">
         <f t="shared" si="2"/>
         <v>🟡 Medio</v>
       </c>
-      <c r="H17" s="46" t="str">
+      <c r="H17" s="23" t="str">
         <f t="shared" si="3"/>
         <v>Mantener</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="B18" s="8">
+      <c r="A18" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B18" s="9">
         <f>SUMPRODUCT(H$28:H$34,$B$3:$B$9)</f>
         <v>63</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D18" s="8">
+      <c r="C18" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D18" s="9">
         <v>100</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="10">
         <f>B18/D18</f>
         <v>0.63</v>
       </c>
-      <c r="F18" s="5" t="str">
+      <c r="F18" s="7" t="str">
         <f t="shared" si="1"/>
         <v>✓ OK</v>
       </c>
-      <c r="G18" s="45" t="str">
+      <c r="G18" s="22" t="str">
         <f t="shared" si="2"/>
         <v>🟡 Medio</v>
       </c>
-      <c r="H18" s="46" t="str">
+      <c r="H18" s="23" t="str">
         <f t="shared" si="3"/>
         <v>Mantener</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="B19" s="8">
+      <c r="A19" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="B19" s="9">
         <f>SUMPRODUCT(I$28:I$34,$B$3:$B$9)</f>
         <v>27</v>
       </c>
-      <c r="C19" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D19" s="8">
+      <c r="C19" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D19" s="9">
         <v>50</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="10">
         <f>B19/D19</f>
         <v>0.54</v>
       </c>
-      <c r="F19" s="5" t="str">
+      <c r="F19" s="7" t="str">
         <f t="shared" si="1"/>
         <v>✓ OK</v>
       </c>
-      <c r="G19" s="45" t="str">
+      <c r="G19" s="22" t="str">
         <f t="shared" si="2"/>
         <v>🟡 Medio</v>
       </c>
-      <c r="H19" s="46" t="str">
+      <c r="H19" s="23" t="str">
         <f t="shared" si="3"/>
         <v>Mantener</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B20" s="8">
+      <c r="A20" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" s="9">
         <f>SUMPRODUCT(J$28:J$34,$B$3:$B$9)</f>
         <v>500</v>
       </c>
-      <c r="C20" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D20" s="8">
+      <c r="C20" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D20" s="9">
         <v>500</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="10">
         <f>B20/D20</f>
         <v>1</v>
       </c>
-      <c r="F20" s="5" t="str">
+      <c r="F20" s="7" t="str">
         <f t="shared" si="1"/>
         <v>✓ OK</v>
       </c>
-      <c r="G20" s="45" t="str">
+      <c r="G20" s="22" t="str">
         <f t="shared" si="2"/>
         <v>🔴 Crítico</v>
       </c>
-      <c r="H20" s="46" t="str">
+      <c r="H20" s="23" t="str">
         <f t="shared" si="3"/>
         <v>Recomienda aumentar</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B22" s="8">
+      <c r="A22" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" s="9">
         <f>B3</f>
         <v>10</v>
       </c>
-      <c r="C22" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="D22" s="8">
+      <c r="C22" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="D22" s="9">
         <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B23" s="8">
+      <c r="A23" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B23" s="9">
         <f>B5</f>
         <v>5</v>
       </c>
-      <c r="C23" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="D23" s="8">
+      <c r="C23" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="D23" s="9">
         <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B24" s="8">
+      <c r="A24" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B24" s="9">
         <f>B8</f>
         <v>9</v>
       </c>
-      <c r="C24" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="D24" s="8">
+      <c r="C24" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="D24" s="9">
         <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="41" t="s">
-        <v>79</v>
+      <c r="A26" s="20" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="39" t="s">
+      <c r="A27" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="B27" s="39" t="s">
-        <v>71</v>
-      </c>
-      <c r="C27" s="39" t="s">
-        <v>80</v>
-      </c>
-      <c r="D27" s="39" t="s">
+      <c r="B27" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="C27" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="E27" s="39" t="s">
-        <v>81</v>
-      </c>
-      <c r="F27" s="39" t="s">
-        <v>82</v>
-      </c>
-      <c r="G27" s="39" t="s">
+      <c r="D27" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="F27" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="G27" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="H27" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="I27" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="J27" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="H27" s="39" t="s">
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" s="7">
+        <v>0.08</v>
+      </c>
+      <c r="C28" s="7">
+        <v>250</v>
+      </c>
+      <c r="D28" s="7">
+        <v>1</v>
+      </c>
+      <c r="E28" s="7">
+        <v>3</v>
+      </c>
+      <c r="F28" s="7">
+        <v>0</v>
+      </c>
+      <c r="G28" s="7">
+        <v>3</v>
+      </c>
+      <c r="H28" s="7">
+        <v>3</v>
+      </c>
+      <c r="I28" s="7">
+        <v>0</v>
+      </c>
+      <c r="J28" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="C29" s="7">
+        <v>250</v>
+      </c>
+      <c r="D29" s="7">
+        <v>0</v>
+      </c>
+      <c r="E29" s="7">
+        <v>3</v>
+      </c>
+      <c r="F29" s="7">
+        <v>0</v>
+      </c>
+      <c r="G29" s="7">
+        <v>3</v>
+      </c>
+      <c r="H29" s="7">
+        <v>3</v>
+      </c>
+      <c r="I29" s="7">
+        <v>0</v>
+      </c>
+      <c r="J29" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B30" s="7">
+        <v>0.06</v>
+      </c>
+      <c r="C30" s="7">
+        <v>250</v>
+      </c>
+      <c r="D30" s="7">
+        <v>0</v>
+      </c>
+      <c r="E30" s="7">
+        <v>3</v>
+      </c>
+      <c r="F30" s="7">
+        <v>0</v>
+      </c>
+      <c r="G30" s="7">
+        <v>3</v>
+      </c>
+      <c r="H30" s="7">
+        <v>3</v>
+      </c>
+      <c r="I30" s="7">
+        <v>0</v>
+      </c>
+      <c r="J30" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B31" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="C31" s="7">
+        <v>250</v>
+      </c>
+      <c r="D31" s="7">
+        <v>1</v>
+      </c>
+      <c r="E31" s="7">
+        <v>3</v>
+      </c>
+      <c r="F31" s="7">
+        <v>0</v>
+      </c>
+      <c r="G31" s="7">
+        <v>3</v>
+      </c>
+      <c r="H31" s="7">
+        <v>3</v>
+      </c>
+      <c r="I31" s="7">
+        <v>0</v>
+      </c>
+      <c r="J31" s="7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B32" s="7">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="C32" s="7">
+        <v>250</v>
+      </c>
+      <c r="D32" s="7">
+        <v>1</v>
+      </c>
+      <c r="E32" s="7">
+        <v>3</v>
+      </c>
+      <c r="F32" s="7">
+        <v>0</v>
+      </c>
+      <c r="G32" s="7">
+        <v>3</v>
+      </c>
+      <c r="H32" s="7">
+        <v>3</v>
+      </c>
+      <c r="I32" s="7">
+        <v>0</v>
+      </c>
+      <c r="J32" s="7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B33" s="7">
+        <v>0</v>
+      </c>
+      <c r="C33" s="7">
+        <v>0</v>
+      </c>
+      <c r="D33" s="7">
+        <v>0</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0</v>
+      </c>
+      <c r="F33" s="7">
+        <v>1</v>
+      </c>
+      <c r="G33" s="7">
+        <v>0</v>
+      </c>
+      <c r="H33" s="7">
+        <v>0</v>
+      </c>
+      <c r="I33" s="7">
+        <v>3</v>
+      </c>
+      <c r="J33" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B34" s="7">
+        <v>0</v>
+      </c>
+      <c r="C34" s="7">
+        <v>1</v>
+      </c>
+      <c r="D34" s="7">
+        <v>0</v>
+      </c>
+      <c r="E34" s="7">
+        <v>0</v>
+      </c>
+      <c r="F34" s="7">
+        <v>1</v>
+      </c>
+      <c r="G34" s="7">
+        <v>0</v>
+      </c>
+      <c r="H34" s="7">
+        <v>0</v>
+      </c>
+      <c r="I34" s="7">
+        <v>0</v>
+      </c>
+      <c r="J34" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="I27" s="39" t="s">
-        <v>95</v>
-      </c>
-      <c r="J27" s="39" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B28" s="5">
-        <v>0.08</v>
-      </c>
-      <c r="C28" s="5">
-        <v>250</v>
-      </c>
-      <c r="D28" s="5">
-        <v>1</v>
-      </c>
-      <c r="E28" s="5">
-        <v>3</v>
-      </c>
-      <c r="F28" s="5">
-        <v>0</v>
-      </c>
-      <c r="G28" s="5">
-        <v>3</v>
-      </c>
-      <c r="H28" s="5">
-        <v>3</v>
-      </c>
-      <c r="I28" s="5">
-        <v>0</v>
-      </c>
-      <c r="J28" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B29" s="5">
-        <v>0.04</v>
-      </c>
-      <c r="C29" s="5">
-        <v>250</v>
-      </c>
-      <c r="D29" s="5">
-        <v>0</v>
-      </c>
-      <c r="E29" s="5">
-        <v>3</v>
-      </c>
-      <c r="F29" s="5">
-        <v>0</v>
-      </c>
-      <c r="G29" s="5">
-        <v>3</v>
-      </c>
-      <c r="H29" s="5">
-        <v>3</v>
-      </c>
-      <c r="I29" s="5">
-        <v>0</v>
-      </c>
-      <c r="J29" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B30" s="5">
-        <v>0.06</v>
-      </c>
-      <c r="C30" s="5">
-        <v>250</v>
-      </c>
-      <c r="D30" s="5">
-        <v>0</v>
-      </c>
-      <c r="E30" s="5">
-        <v>3</v>
-      </c>
-      <c r="F30" s="5">
-        <v>0</v>
-      </c>
-      <c r="G30" s="5">
-        <v>3</v>
-      </c>
-      <c r="H30" s="5">
-        <v>3</v>
-      </c>
-      <c r="I30" s="5">
-        <v>0</v>
-      </c>
-      <c r="J30" s="5">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B31" s="5">
-        <v>0.04</v>
-      </c>
-      <c r="C31" s="5">
-        <v>250</v>
-      </c>
-      <c r="D31" s="5">
-        <v>1</v>
-      </c>
-      <c r="E31" s="5">
-        <v>3</v>
-      </c>
-      <c r="F31" s="5">
-        <v>0</v>
-      </c>
-      <c r="G31" s="5">
-        <v>3</v>
-      </c>
-      <c r="H31" s="5">
-        <v>3</v>
-      </c>
-      <c r="I31" s="5">
-        <v>0</v>
-      </c>
-      <c r="J31" s="5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B32" s="5">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="C32" s="5">
-        <v>250</v>
-      </c>
-      <c r="D32" s="5">
-        <v>1</v>
-      </c>
-      <c r="E32" s="5">
-        <v>3</v>
-      </c>
-      <c r="F32" s="5">
-        <v>0</v>
-      </c>
-      <c r="G32" s="5">
-        <v>3</v>
-      </c>
-      <c r="H32" s="5">
-        <v>3</v>
-      </c>
-      <c r="I32" s="5">
-        <v>0</v>
-      </c>
-      <c r="J32" s="5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B33" s="5">
-        <v>0</v>
-      </c>
-      <c r="C33" s="5">
-        <v>0</v>
-      </c>
-      <c r="D33" s="5">
-        <v>0</v>
-      </c>
-      <c r="E33" s="5">
-        <v>0</v>
-      </c>
-      <c r="F33" s="5">
-        <v>1</v>
-      </c>
-      <c r="G33" s="5">
-        <v>0</v>
-      </c>
-      <c r="H33" s="5">
-        <v>0</v>
-      </c>
-      <c r="I33" s="5">
-        <v>3</v>
-      </c>
-      <c r="J33" s="5">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B34" s="5">
-        <v>0</v>
-      </c>
-      <c r="C34" s="5">
-        <v>0</v>
-      </c>
-      <c r="D34" s="5">
-        <v>0</v>
-      </c>
-      <c r="E34" s="5">
-        <v>0</v>
-      </c>
-      <c r="F34" s="5">
-        <v>1</v>
-      </c>
-      <c r="G34" s="5">
-        <v>0</v>
-      </c>
-      <c r="H34" s="5">
-        <v>0</v>
-      </c>
-      <c r="I34" s="5">
-        <v>0</v>
-      </c>
-      <c r="J34" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="39" t="s">
-        <v>84</v>
-      </c>
-      <c r="B36" s="11">
+      <c r="B36" s="12">
         <f>SUMPRODUCT(B3:B9,B39:B45)</f>
         <v>963</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="10"/>
+      <c r="A37" s="11"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="43" t="s">
-        <v>85</v>
-      </c>
-      <c r="B38" s="44"/>
+      <c r="A38" s="63" t="s">
+        <v>98</v>
+      </c>
+      <c r="B38" s="64"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="B39" s="5">
+      <c r="A39" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B39" s="7">
         <v>22</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="B40" s="5">
+      <c r="A40" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="B40" s="7">
         <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="B41" s="5">
+      <c r="A41" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B41" s="7">
         <v>25</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="B42" s="5">
+      <c r="A42" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B42" s="7">
         <v>30</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="B43" s="5">
+      <c r="A43" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B43" s="7">
         <v>28</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="B44" s="5">
+      <c r="A44" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="B44" s="7">
         <v>30</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="B45" s="5">
+      <c r="A45" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B45" s="7">
         <v>15</v>
       </c>
     </row>
@@ -4071,4 +4065,1003 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89B5F9BD-C155-452C-AFB9-B117A8C08C65}">
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="2.28515625" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B7" s="32"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="32" t="s">
+        <v>147</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>149</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>151</v>
+      </c>
+      <c r="G7" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="H7" s="32" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="33" t="s">
+        <v>145</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>146</v>
+      </c>
+      <c r="D8" s="33" t="s">
+        <v>148</v>
+      </c>
+      <c r="E8" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="F8" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="G8" s="33" t="s">
+        <v>154</v>
+      </c>
+      <c r="H8" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="I8" s="34" t="s">
+        <v>199</v>
+      </c>
+      <c r="J8" s="34" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B9" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>162</v>
+      </c>
+      <c r="D9" s="30">
+        <v>5</v>
+      </c>
+      <c r="E9" s="30">
+        <v>0</v>
+      </c>
+      <c r="F9" s="30">
+        <v>22</v>
+      </c>
+      <c r="G9" s="30">
+        <v>3.9999999999999969</v>
+      </c>
+      <c r="H9" s="30">
+        <v>1E+30</v>
+      </c>
+      <c r="I9">
+        <f>F9-H9</f>
+        <v>-1E+30</v>
+      </c>
+      <c r="J9">
+        <f>F9+G9</f>
+        <v>25.999999999999996</v>
+      </c>
+      <c r="N9" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B10" s="30" t="s">
+        <v>163</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>164</v>
+      </c>
+      <c r="D10" s="30">
+        <v>0</v>
+      </c>
+      <c r="E10" s="30">
+        <v>-5.9999999999999964</v>
+      </c>
+      <c r="F10" s="30">
+        <v>20</v>
+      </c>
+      <c r="G10" s="30">
+        <v>5.9999999999999964</v>
+      </c>
+      <c r="H10" s="30">
+        <v>1E+30</v>
+      </c>
+      <c r="I10">
+        <f t="shared" ref="I10:I31" si="0">F10-H10</f>
+        <v>-1E+30</v>
+      </c>
+      <c r="J10">
+        <f t="shared" ref="J10:J31" si="1">F10+G10</f>
+        <v>25.999999999999996</v>
+      </c>
+      <c r="N10" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B11" s="30" t="s">
+        <v>165</v>
+      </c>
+      <c r="C11" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="D11" s="30">
+        <v>5</v>
+      </c>
+      <c r="E11" s="30">
+        <v>0</v>
+      </c>
+      <c r="F11" s="30">
+        <v>25</v>
+      </c>
+      <c r="G11" s="30">
+        <v>10.999999999999998</v>
+      </c>
+      <c r="H11" s="30">
+        <v>1E+30</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="0"/>
+        <v>-1E+30</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="N11" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B12" s="30" t="s">
+        <v>167</v>
+      </c>
+      <c r="C12" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="D12" s="30">
+        <v>12</v>
+      </c>
+      <c r="E12" s="30">
+        <v>0</v>
+      </c>
+      <c r="F12" s="30">
+        <v>30</v>
+      </c>
+      <c r="G12" s="30">
+        <v>3.6028797018964E+16</v>
+      </c>
+      <c r="H12" s="30">
+        <v>2</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="1"/>
+        <v>3.6028797018964032E+16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B13" s="30" t="s">
+        <v>169</v>
+      </c>
+      <c r="C13" s="30" t="s">
+        <v>170</v>
+      </c>
+      <c r="D13" s="30">
+        <v>0</v>
+      </c>
+      <c r="E13" s="30">
+        <v>-2</v>
+      </c>
+      <c r="F13" s="30">
+        <v>28</v>
+      </c>
+      <c r="G13" s="30">
+        <v>2</v>
+      </c>
+      <c r="H13" s="30">
+        <v>1E+30</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="0"/>
+        <v>-1E+30</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B14" s="30" t="s">
+        <v>171</v>
+      </c>
+      <c r="C14" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="D14" s="30">
+        <v>15.399999999999999</v>
+      </c>
+      <c r="E14" s="30">
+        <v>0</v>
+      </c>
+      <c r="F14" s="30">
+        <v>30</v>
+      </c>
+      <c r="G14" s="30">
+        <v>7.4999999999999973</v>
+      </c>
+      <c r="H14" s="30">
+        <v>7.5723472668810254</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="0"/>
+        <v>22.427652733118975</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="1"/>
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="31" t="s">
+        <v>173</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>174</v>
+      </c>
+      <c r="D15" s="31">
+        <v>0</v>
+      </c>
+      <c r="E15" s="31">
+        <v>-5.0239999999999974</v>
+      </c>
+      <c r="F15" s="31">
+        <v>15</v>
+      </c>
+      <c r="G15" s="31">
+        <v>5.0239999999999974</v>
+      </c>
+      <c r="H15" s="31">
+        <v>1E+30</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="0"/>
+        <v>-1E+30</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="1"/>
+        <v>20.023999999999997</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B18" s="32"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32" t="s">
+        <v>147</v>
+      </c>
+      <c r="E18" s="32" t="s">
+        <v>157</v>
+      </c>
+      <c r="F18" s="32" t="s">
+        <v>159</v>
+      </c>
+      <c r="G18" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="H18" s="32" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="33" t="s">
+        <v>145</v>
+      </c>
+      <c r="C19" s="33" t="s">
+        <v>146</v>
+      </c>
+      <c r="D19" s="33" t="s">
+        <v>148</v>
+      </c>
+      <c r="E19" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="F19" s="33" t="s">
+        <v>160</v>
+      </c>
+      <c r="G19" s="33" t="s">
+        <v>154</v>
+      </c>
+      <c r="H19" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="I19" s="34" t="s">
+        <v>199</v>
+      </c>
+      <c r="J19" s="34" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B20" s="30" t="s">
+        <v>175</v>
+      </c>
+      <c r="C20" s="30" t="s">
+        <v>176</v>
+      </c>
+      <c r="D20" s="30">
+        <v>1.18</v>
+      </c>
+      <c r="E20" s="30">
+        <v>0</v>
+      </c>
+      <c r="F20" s="30">
+        <v>3</v>
+      </c>
+      <c r="G20" s="30">
+        <v>1E+30</v>
+      </c>
+      <c r="H20" s="30">
+        <v>1.8200000000000003</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="0"/>
+        <v>1.1799999999999997</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="1"/>
+        <v>1E+30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B21" s="30" t="s">
+        <v>177</v>
+      </c>
+      <c r="C21" s="30" t="s">
+        <v>178</v>
+      </c>
+      <c r="D21" s="30">
+        <v>5500</v>
+      </c>
+      <c r="E21" s="30">
+        <v>2.3999999999999994E-2</v>
+      </c>
+      <c r="F21" s="30">
+        <v>5500</v>
+      </c>
+      <c r="G21" s="30">
+        <v>333.33333333333366</v>
+      </c>
+      <c r="H21" s="30">
+        <v>395.83333333333303</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="0"/>
+        <v>5104.166666666667</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="1"/>
+        <v>5833.3333333333339</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B22" s="30" t="s">
+        <v>179</v>
+      </c>
+      <c r="C22" s="30" t="s">
+        <v>180</v>
+      </c>
+      <c r="D22" s="30">
+        <v>17</v>
+      </c>
+      <c r="E22" s="30">
+        <v>0</v>
+      </c>
+      <c r="F22" s="30">
+        <v>30</v>
+      </c>
+      <c r="G22" s="30">
+        <v>1E+30</v>
+      </c>
+      <c r="H22" s="30">
+        <v>13</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="1"/>
+        <v>1E+30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B23" s="30" t="s">
+        <v>181</v>
+      </c>
+      <c r="C23" s="30" t="s">
+        <v>182</v>
+      </c>
+      <c r="D23" s="30">
+        <v>66</v>
+      </c>
+      <c r="E23" s="30">
+        <v>0</v>
+      </c>
+      <c r="F23" s="30">
+        <v>70</v>
+      </c>
+      <c r="G23" s="30">
+        <v>1E+30</v>
+      </c>
+      <c r="H23" s="30">
+        <v>4.0000000000000036</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="0"/>
+        <v>66</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="1"/>
+        <v>1E+30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B24" s="30" t="s">
+        <v>183</v>
+      </c>
+      <c r="C24" s="30" t="s">
+        <v>184</v>
+      </c>
+      <c r="D24" s="30">
+        <v>15.399999999999999</v>
+      </c>
+      <c r="E24" s="30">
+        <v>0</v>
+      </c>
+      <c r="F24" s="30">
+        <v>30</v>
+      </c>
+      <c r="G24" s="30">
+        <v>1E+30</v>
+      </c>
+      <c r="H24" s="30">
+        <v>14.6</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="0"/>
+        <v>15.4</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="1"/>
+        <v>1E+30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B25" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="C25" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="D25" s="30">
+        <v>66</v>
+      </c>
+      <c r="E25" s="30">
+        <v>0</v>
+      </c>
+      <c r="F25" s="30">
+        <v>100</v>
+      </c>
+      <c r="G25" s="30">
+        <v>1E+30</v>
+      </c>
+      <c r="H25" s="30">
+        <v>34</v>
+      </c>
+      <c r="I25">
+        <f t="shared" si="0"/>
+        <v>66</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="1"/>
+        <v>1E+30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B26" s="30" t="s">
+        <v>187</v>
+      </c>
+      <c r="C26" s="30" t="s">
+        <v>188</v>
+      </c>
+      <c r="D26" s="30">
+        <v>66</v>
+      </c>
+      <c r="E26" s="30">
+        <v>0</v>
+      </c>
+      <c r="F26" s="30">
+        <v>100</v>
+      </c>
+      <c r="G26" s="30">
+        <v>1E+30</v>
+      </c>
+      <c r="H26" s="30">
+        <v>34</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="0"/>
+        <v>66</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="1"/>
+        <v>1E+30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B27" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="C27" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="D27" s="30">
+        <v>46.199999999999996</v>
+      </c>
+      <c r="E27" s="30">
+        <v>0</v>
+      </c>
+      <c r="F27" s="30">
+        <v>50</v>
+      </c>
+      <c r="G27" s="30">
+        <v>1E+30</v>
+      </c>
+      <c r="H27" s="30">
+        <v>3.7999999999999976</v>
+      </c>
+      <c r="I27">
+        <f t="shared" si="0"/>
+        <v>46.2</v>
+      </c>
+      <c r="J27">
+        <f t="shared" si="1"/>
+        <v>1E+30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B28" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="C28" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="D28" s="30">
+        <v>500</v>
+      </c>
+      <c r="E28" s="30">
+        <v>1.9999999999999998</v>
+      </c>
+      <c r="F28" s="30">
+        <v>500</v>
+      </c>
+      <c r="G28" s="30">
+        <v>18.999999999999986</v>
+      </c>
+      <c r="H28" s="30">
+        <v>186</v>
+      </c>
+      <c r="I28">
+        <f t="shared" si="0"/>
+        <v>314</v>
+      </c>
+      <c r="J28">
+        <f t="shared" si="1"/>
+        <v>519</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B29" s="30" t="s">
+        <v>193</v>
+      </c>
+      <c r="C29" s="30" t="s">
+        <v>194</v>
+      </c>
+      <c r="D29" s="30">
+        <v>5</v>
+      </c>
+      <c r="E29" s="30">
+        <v>-3.9999999999999969</v>
+      </c>
+      <c r="F29" s="30">
+        <v>5</v>
+      </c>
+      <c r="G29" s="30">
+        <v>9.4999999999999911</v>
+      </c>
+      <c r="H29" s="30">
+        <v>5</v>
+      </c>
+      <c r="I29">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <f t="shared" si="1"/>
+        <v>14.499999999999991</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B30" s="30" t="s">
+        <v>195</v>
+      </c>
+      <c r="C30" s="30" t="s">
+        <v>196</v>
+      </c>
+      <c r="D30" s="30">
+        <v>5</v>
+      </c>
+      <c r="E30" s="30">
+        <v>-10.999999999999998</v>
+      </c>
+      <c r="F30" s="30">
+        <v>5</v>
+      </c>
+      <c r="G30" s="30">
+        <v>12.000000000000004</v>
+      </c>
+      <c r="H30" s="30">
+        <v>5</v>
+      </c>
+      <c r="I30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <f t="shared" si="1"/>
+        <v>17.000000000000004</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="31" t="s">
+        <v>197</v>
+      </c>
+      <c r="C31" s="31" t="s">
+        <v>198</v>
+      </c>
+      <c r="D31" s="31">
+        <v>15.399999999999999</v>
+      </c>
+      <c r="E31" s="31">
+        <v>0</v>
+      </c>
+      <c r="F31" s="31">
+        <v>3</v>
+      </c>
+      <c r="G31" s="31">
+        <v>12.4</v>
+      </c>
+      <c r="H31" s="31">
+        <v>1E+30</v>
+      </c>
+      <c r="I31">
+        <f t="shared" si="0"/>
+        <v>-1E+30</v>
+      </c>
+      <c r="J31">
+        <f t="shared" si="1"/>
+        <v>15.4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D82E5C12-CA29-4BF2-976C-69332C5FF0C6}">
+  <dimension ref="A2:J17"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="16.140625" customWidth="1"/>
+    <col min="3" max="3" width="22.5703125" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" customWidth="1"/>
+    <col min="7" max="7" width="7.140625" customWidth="1"/>
+    <col min="8" max="8" width="15.85546875" customWidth="1"/>
+    <col min="9" max="9" width="7.5703125" customWidth="1"/>
+    <col min="10" max="10" width="5.7109375" customWidth="1"/>
+    <col min="11" max="11" width="9.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C2" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="G2" s="65">
+        <v>5.5</v>
+      </c>
+      <c r="H2" s="66" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C3" s="69" t="s">
+        <v>207</v>
+      </c>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="G3" s="65">
+        <v>60</v>
+      </c>
+      <c r="H3" s="66" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C4" s="35" t="s">
+        <v>210</v>
+      </c>
+      <c r="D4" s="36" t="s">
+        <v>208</v>
+      </c>
+      <c r="E4" s="35" t="s">
+        <v>209</v>
+      </c>
+      <c r="F4" s="11"/>
+      <c r="G4" s="65">
+        <f>G2*G3</f>
+        <v>330</v>
+      </c>
+      <c r="H4" s="37" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>8</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>201</v>
+      </c>
+      <c r="C5" s="35">
+        <v>3</v>
+      </c>
+      <c r="D5" s="36">
+        <v>3</v>
+      </c>
+      <c r="E5" s="35">
+        <v>0.5</v>
+      </c>
+      <c r="G5" s="70">
+        <v>20</v>
+      </c>
+      <c r="H5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>7</v>
+      </c>
+      <c r="B6" s="35" t="s">
+        <v>202</v>
+      </c>
+      <c r="C6" s="35">
+        <v>6</v>
+      </c>
+      <c r="D6" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="E6" s="35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>203</v>
+      </c>
+      <c r="C7" s="35">
+        <v>3</v>
+      </c>
+      <c r="D7" s="36">
+        <v>3</v>
+      </c>
+      <c r="E7" s="35">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C10" s="69" t="s">
+        <v>211</v>
+      </c>
+      <c r="D10" s="69"/>
+      <c r="E10" s="69"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C11" s="35" t="s">
+        <v>210</v>
+      </c>
+      <c r="D11" s="36" t="s">
+        <v>208</v>
+      </c>
+      <c r="E11" s="35" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B12" s="35" t="s">
+        <v>201</v>
+      </c>
+      <c r="C12" s="7">
+        <v>7</v>
+      </c>
+      <c r="D12" s="22">
+        <v>0</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1</v>
+      </c>
+      <c r="F12" s="68">
+        <f>SUM(C12:E12)</f>
+        <v>8</v>
+      </c>
+      <c r="G12" s="68" t="s">
+        <v>213</v>
+      </c>
+      <c r="H12" s="68">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B13" s="35" t="s">
+        <v>202</v>
+      </c>
+      <c r="C13" s="7">
+        <v>1</v>
+      </c>
+      <c r="D13" s="22">
+        <v>5</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1</v>
+      </c>
+      <c r="F13" s="68">
+        <f>SUM(C13:E13)</f>
+        <v>7</v>
+      </c>
+      <c r="G13" s="68" t="s">
+        <v>213</v>
+      </c>
+      <c r="H13" s="68">
+        <v>7</v>
+      </c>
+      <c r="I13" s="67" t="s">
+        <v>212</v>
+      </c>
+      <c r="J13" s="67">
+        <f>SUMPRODUCT(C5:E7,C12:E14)</f>
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B14" s="35" t="s">
+        <v>203</v>
+      </c>
+      <c r="C14" s="7">
+        <v>0</v>
+      </c>
+      <c r="D14" s="22">
+        <v>0</v>
+      </c>
+      <c r="E14" s="7">
+        <v>5</v>
+      </c>
+      <c r="F14" s="68">
+        <f>SUM(C14:E14)</f>
+        <v>5</v>
+      </c>
+      <c r="G14" s="68" t="s">
+        <v>213</v>
+      </c>
+      <c r="H14" s="68">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C15" s="68">
+        <f>C12+C13+C14</f>
+        <v>8</v>
+      </c>
+      <c r="D15" s="68">
+        <f>D12+D13+D14</f>
+        <v>5</v>
+      </c>
+      <c r="E15" s="68">
+        <f>E12+E13+E14</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C16" s="68" t="s">
+        <v>213</v>
+      </c>
+      <c r="D16" s="68" t="s">
+        <v>213</v>
+      </c>
+      <c r="E16" s="68" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="17" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C17" s="68">
+        <v>8</v>
+      </c>
+      <c r="D17" s="68">
+        <v>5</v>
+      </c>
+      <c r="E17" s="68">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="C10:E10"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Excel/InvOperativa_FINAL.xlsx
+++ b/Excel/InvOperativa_FINAL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rick\Documents\GitHub\InvestigacionOperativaExcel\yarimashita\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{75FC1AFD-F82D-4126-A285-D8C2412BE2DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{079962FA-9037-42A3-AADA-00105993B0AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Modelo" sheetId="1" r:id="rId1"/>
@@ -111,7 +111,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="220">
   <si>
     <t>MAKI &amp; RAMEN HOUSE</t>
   </si>
@@ -768,13 +768,16 @@
   </si>
   <si>
     <t>Sacos por Local</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRESENTACION : https://investigacion-operativa-liard.vercel.app/transporte.html </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -898,6 +901,14 @@
       <b/>
       <sz val="11"/>
       <color indexed="18"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1333,11 +1344,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1398,8 +1410,47 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1412,34 +1463,11 @@
     <xf numFmtId="0" fontId="6" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="16" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1459,24 +1487,12 @@
     <xf numFmtId="0" fontId="16" fillId="17" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
@@ -1802,96 +1818,106 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
+      <c r="A1" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="39"/>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
+      <c r="A2" s="45"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
     </row>
     <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="39"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="39"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="39"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
     </row>
     <row r="6" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="49" t="s">
+      <c r="A7" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="50"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50"/>
-      <c r="F7" s="51"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="50"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="52"/>
-      <c r="B8" s="39"/>
-      <c r="C8" s="39"/>
-      <c r="D8" s="39"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="53"/>
+      <c r="A8" s="51"/>
+      <c r="B8" s="45"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="52"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="54"/>
-      <c r="B9" s="55"/>
-      <c r="C9" s="55"/>
-      <c r="D9" s="55"/>
-      <c r="E9" s="55"/>
-      <c r="F9" s="56"/>
+      <c r="A9" s="53"/>
+      <c r="B9" s="54"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="55"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="71" t="s">
+        <v>219</v>
+      </c>
+      <c r="B10" s="71"/>
+      <c r="C10" s="71"/>
+      <c r="D10" s="71"/>
+      <c r="E10" s="71"/>
+      <c r="F10" s="71"/>
     </row>
     <row r="13" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="44" t="s">
+      <c r="A13" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="B13" s="39"/>
-      <c r="C13" s="39"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="39"/>
+      <c r="B13" s="45"/>
+      <c r="C13" s="45"/>
+      <c r="D13" s="45"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
     </row>
     <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="48" t="s">
+      <c r="A15" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="48"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="48"/>
+      <c r="B15" s="46"/>
+      <c r="C15" s="46"/>
+      <c r="D15" s="46"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
@@ -2006,48 +2032,48 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="38" t="s">
+      <c r="A24" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="39"/>
-      <c r="C24" s="39"/>
-      <c r="D24" s="39"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="45"/>
+      <c r="D24" s="45"/>
     </row>
     <row r="27" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="46" t="s">
+      <c r="A27" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="B27" s="46"/>
-      <c r="C27" s="46"/>
-      <c r="D27" s="46"/>
-      <c r="E27" s="46"/>
+      <c r="B27" s="64"/>
+      <c r="C27" s="64"/>
+      <c r="D27" s="64"/>
+      <c r="E27" s="64"/>
     </row>
     <row r="28" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="45" t="s">
+      <c r="A28" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="B28" s="45"/>
-      <c r="C28" s="45"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="45"/>
+      <c r="B28" s="63"/>
+      <c r="C28" s="63"/>
+      <c r="D28" s="63"/>
+      <c r="E28" s="63"/>
     </row>
     <row r="29" spans="1:5" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A29" s="40" t="s">
+      <c r="A29" s="59" t="s">
         <v>30</v>
       </c>
-      <c r="B29" s="41"/>
-      <c r="C29" s="41"/>
-      <c r="D29" s="41"/>
-      <c r="E29" s="42"/>
+      <c r="B29" s="60"/>
+      <c r="C29" s="60"/>
+      <c r="D29" s="60"/>
+      <c r="E29" s="61"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="38" t="s">
+      <c r="A30" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="B30" s="39"/>
-      <c r="C30" s="39"/>
-      <c r="D30" s="39"/>
-      <c r="E30" s="39"/>
+      <c r="B30" s="45"/>
+      <c r="C30" s="45"/>
+      <c r="D30" s="45"/>
+      <c r="E30" s="45"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
@@ -2138,14 +2164,14 @@
       </c>
     </row>
     <row r="41" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="43" t="s">
+      <c r="A41" s="62" t="s">
         <v>33</v>
       </c>
-      <c r="B41" s="43"/>
-      <c r="C41" s="43"/>
-      <c r="D41" s="43"/>
-      <c r="E41" s="43"/>
-      <c r="F41" s="43"/>
+      <c r="B41" s="62"/>
+      <c r="C41" s="62"/>
+      <c r="D41" s="62"/>
+      <c r="E41" s="62"/>
+      <c r="F41" s="62"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
@@ -2408,7 +2434,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A27:E27"/>
     <mergeCell ref="A1:F2"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A6:F6"/>
@@ -2416,13 +2448,11 @@
     <mergeCell ref="A24:D24"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="A41:F41"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A10:F10"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A10:F10" r:id="rId1" display="PRESENTACION : https://investigacion-operativa-liard.vercel.app/transporte.html " xr:uid="{CB9A5D92-35C5-4B51-A251-891D41E8861D}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2444,18 +2474,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="65" t="s">
         <v>125</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="62"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="68"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
@@ -3178,10 +3208,10 @@
       <c r="A37" s="11"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="63" t="s">
+      <c r="A38" s="69" t="s">
         <v>98</v>
       </c>
-      <c r="B38" s="64"/>
+      <c r="B38" s="70"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
@@ -3266,18 +3296,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="65" t="s">
         <v>128</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="62"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="68"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
@@ -3997,10 +4027,10 @@
       <c r="A37" s="11"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="63" t="s">
+      <c r="A38" s="69" t="s">
         <v>98</v>
       </c>
-      <c r="B38" s="64"/>
+      <c r="B38" s="70"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
@@ -4828,23 +4858,23 @@
       <c r="C2" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="G2" s="65">
+      <c r="G2" s="38">
         <v>5.5</v>
       </c>
-      <c r="H2" s="66" t="s">
+      <c r="H2" s="39" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C3" s="69" t="s">
+      <c r="C3" s="43" t="s">
         <v>207</v>
       </c>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="G3" s="65">
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="G3" s="38">
         <v>60</v>
       </c>
-      <c r="H3" s="66" t="s">
+      <c r="H3" s="39" t="s">
         <v>217</v>
       </c>
     </row>
@@ -4859,7 +4889,7 @@
         <v>209</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="65">
+      <c r="G4" s="38">
         <f>G2*G3</f>
         <v>330</v>
       </c>
@@ -4883,7 +4913,7 @@
       <c r="E5" s="35">
         <v>0.5</v>
       </c>
-      <c r="G5" s="70">
+      <c r="G5" s="42">
         <v>20</v>
       </c>
       <c r="H5" t="s">
@@ -4925,11 +4955,11 @@
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C10" s="69" t="s">
+      <c r="C10" s="43" t="s">
         <v>211</v>
       </c>
-      <c r="D10" s="69"/>
-      <c r="E10" s="69"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="C11" s="35" t="s">
@@ -4955,14 +4985,14 @@
       <c r="E12" s="7">
         <v>1</v>
       </c>
-      <c r="F12" s="68">
+      <c r="F12" s="41">
         <f>SUM(C12:E12)</f>
         <v>8</v>
       </c>
-      <c r="G12" s="68" t="s">
+      <c r="G12" s="41" t="s">
         <v>213</v>
       </c>
-      <c r="H12" s="68">
+      <c r="H12" s="41">
         <v>8</v>
       </c>
     </row>
@@ -4979,20 +5009,20 @@
       <c r="E13" s="7">
         <v>1</v>
       </c>
-      <c r="F13" s="68">
+      <c r="F13" s="41">
         <f>SUM(C13:E13)</f>
         <v>7</v>
       </c>
-      <c r="G13" s="68" t="s">
+      <c r="G13" s="41" t="s">
         <v>213</v>
       </c>
-      <c r="H13" s="68">
+      <c r="H13" s="41">
         <v>7</v>
       </c>
-      <c r="I13" s="67" t="s">
+      <c r="I13" s="40" t="s">
         <v>212</v>
       </c>
-      <c r="J13" s="67">
+      <c r="J13" s="40">
         <f>SUMPRODUCT(C5:E7,C12:E14)</f>
         <v>35.5</v>
       </c>
@@ -5010,50 +5040,50 @@
       <c r="E14" s="7">
         <v>5</v>
       </c>
-      <c r="F14" s="68">
+      <c r="F14" s="41">
         <f>SUM(C14:E14)</f>
         <v>5</v>
       </c>
-      <c r="G14" s="68" t="s">
+      <c r="G14" s="41" t="s">
         <v>213</v>
       </c>
-      <c r="H14" s="68">
+      <c r="H14" s="41">
         <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C15" s="68">
+      <c r="C15" s="41">
         <f>C12+C13+C14</f>
         <v>8</v>
       </c>
-      <c r="D15" s="68">
+      <c r="D15" s="41">
         <f>D12+D13+D14</f>
         <v>5</v>
       </c>
-      <c r="E15" s="68">
+      <c r="E15" s="41">
         <f>E12+E13+E14</f>
         <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C16" s="68" t="s">
+      <c r="C16" s="41" t="s">
         <v>213</v>
       </c>
-      <c r="D16" s="68" t="s">
+      <c r="D16" s="41" t="s">
         <v>213</v>
       </c>
-      <c r="E16" s="68" t="s">
+      <c r="E16" s="41" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="17" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C17" s="68">
+      <c r="C17" s="41">
         <v>8</v>
       </c>
-      <c r="D17" s="68">
+      <c r="D17" s="41">
         <v>5</v>
       </c>
-      <c r="E17" s="68">
+      <c r="E17" s="41">
         <v>7</v>
       </c>
     </row>
